--- a/templates/excel/yukleme_plani_template.xlsx
+++ b/templates/excel/yukleme_plani_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>ŞOFÖR ADI</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>NET</t>
+  </si>
+  <si>
+    <t>ADET</t>
   </si>
 </sst>
 </file>
@@ -1221,6 +1224,7 @@
     <col min="3" max="3" width="13.046875" customWidth="true" style="0"/>
     <col min="7" max="7" width="10.89453125" customWidth="true" style="0"/>
     <col min="9" max="9" width="9.28125" customWidth="true" style="0"/>
+    <col min="11" max="11" width="9.10" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" customHeight="1" ht="29.25">
@@ -2037,7 +2041,9 @@
       <c r="K37" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="L37" s="70"/>
+      <c r="L37" s="32" t="s">
+        <v>52</v>
+      </c>
       <c r="M37" s="26"/>
       <c r="N37" s="27"/>
       <c r="O37" s="75"/>

--- a/templates/excel/yukleme_plani_template.xlsx
+++ b/templates/excel/yukleme_plani_template.xlsx
@@ -405,7 +405,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -523,17 +523,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -557,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="132">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -730,9 +719,6 @@
     <xf xfId="0" fontId="7" numFmtId="164" fillId="9" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="164" fillId="9" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="7" numFmtId="3" fillId="9" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -871,13 +857,13 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="2" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="2" numFmtId="14" fillId="2" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="2" borderId="12" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1224,170 +1210,170 @@
     <col min="3" max="3" width="13.046875" customWidth="true" style="0"/>
     <col min="7" max="7" width="10.89453125" customWidth="true" style="0"/>
     <col min="9" max="9" width="9.28125" customWidth="true" style="0"/>
-    <col min="11" max="11" width="9.10" style="0"/>
+    <col min="11" max="11" width="9.1" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" customHeight="1" ht="29.25">
-      <c r="A1" s="115"/>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
+      <c r="A1" s="114"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
       <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="120"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
       <c r="I3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
+      <c r="J3" s="124"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="120"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
       <c r="I4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="126"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="128"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="127"/>
       <c r="N4" s="5"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
       <c r="I5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="126"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="130"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="129"/>
       <c r="N5" s="5"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
       <c r="I6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="132"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="107"/>
+      <c r="J6" s="131"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="106"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="120"/>
     </row>
     <row r="7" spans="1:16" customHeight="1" ht="18.75">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="98"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="97"/>
       <c r="I7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="132"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="103"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="102"/>
     </row>
     <row r="8" spans="1:16" customHeight="1" ht="18.75">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="98"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
       <c r="I8" s="50"/>
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
@@ -1422,10 +1408,10 @@
       <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="104" t="s">
+      <c r="I9" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="105"/>
+      <c r="J9" s="104"/>
       <c r="K9" s="10" t="s">
         <v>22</v>
       </c>
@@ -1444,20 +1430,20 @@
       <c r="F10" s="15"/>
       <c r="G10" s="53"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="108"/>
+      <c r="J10" s="107"/>
       <c r="K10" s="16"/>
-      <c r="L10" s="109" t="s">
+      <c r="L10" s="108" t="s">
         <v>24</v>
       </c>
       <c r="M10" s="17" t="s">
         <v>25</v>
       </c>
       <c r="N10" s="18"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="114"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="113"/>
     </row>
     <row r="11" spans="1:16" customHeight="1" ht="18.75">
       <c r="A11" s="12"/>
@@ -1473,13 +1459,13 @@
       </c>
       <c r="J11" s="59"/>
       <c r="K11" s="16"/>
-      <c r="L11" s="110"/>
+      <c r="L11" s="109"/>
       <c r="M11" s="17" t="s">
         <v>27</v>
       </c>
       <c r="N11" s="18"/>
-      <c r="O11" s="112"/>
-      <c r="P11" s="114"/>
+      <c r="O11" s="111"/>
+      <c r="P11" s="113"/>
     </row>
     <row r="12" spans="1:16" customHeight="1" ht="18.75">
       <c r="A12" s="12"/>
@@ -1495,13 +1481,13 @@
       </c>
       <c r="J12" s="59"/>
       <c r="K12" s="16"/>
-      <c r="L12" s="110"/>
+      <c r="L12" s="109"/>
       <c r="M12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="N12" s="18"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="113"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="112"/>
     </row>
     <row r="13" spans="1:16" customHeight="1" ht="18.75">
       <c r="A13" s="12"/>
@@ -1517,13 +1503,13 @@
       </c>
       <c r="J13" s="59"/>
       <c r="K13" s="16"/>
-      <c r="L13" s="111"/>
+      <c r="L13" s="110"/>
       <c r="M13" s="17" t="s">
         <v>14</v>
       </c>
       <c r="N13" s="18"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="113"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="112"/>
     </row>
     <row r="14" spans="1:16" customHeight="1" ht="18.75">
       <c r="A14" s="12"/>
@@ -1539,15 +1525,15 @@
       </c>
       <c r="J14" s="59"/>
       <c r="K14" s="16"/>
-      <c r="L14" s="87" t="s">
+      <c r="L14" s="86" t="s">
         <v>31</v>
       </c>
       <c r="M14" s="19" t="s">
         <v>25</v>
       </c>
       <c r="N14" s="20"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
+      <c r="O14" s="89"/>
+      <c r="P14" s="90"/>
     </row>
     <row r="15" spans="1:16" customHeight="1" ht="18.75">
       <c r="A15" s="12"/>
@@ -1558,18 +1544,18 @@
       <c r="F15" s="15"/>
       <c r="G15" s="53"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="92" t="s">
+      <c r="I15" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="93"/>
+      <c r="J15" s="92"/>
       <c r="K15" s="16"/>
-      <c r="L15" s="88"/>
+      <c r="L15" s="87"/>
       <c r="M15" s="19" t="s">
         <v>27</v>
       </c>
       <c r="N15" s="20"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="91"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="90"/>
     </row>
     <row r="16" spans="1:16" customHeight="1" ht="18.75">
       <c r="A16" s="47"/>
@@ -1585,13 +1571,13 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="88"/>
+      <c r="L16" s="87"/>
       <c r="M16" s="19" t="s">
         <v>20</v>
       </c>
       <c r="N16" s="20"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="91"/>
+      <c r="O16" s="89"/>
+      <c r="P16" s="90"/>
     </row>
     <row r="17" spans="1:16" customHeight="1" ht="18.75">
       <c r="A17" s="12"/>
@@ -1607,13 +1593,13 @@
       </c>
       <c r="J17" s="59"/>
       <c r="K17" s="16"/>
-      <c r="L17" s="89"/>
+      <c r="L17" s="88"/>
       <c r="M17" s="19" t="s">
         <v>14</v>
       </c>
       <c r="N17" s="20"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="91"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="90"/>
     </row>
     <row r="18" spans="1:16" customHeight="1" ht="21">
       <c r="A18" s="12"/>
@@ -1629,15 +1615,15 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="16"/>
-      <c r="L18" s="78" t="s">
+      <c r="L18" s="77" t="s">
         <v>36</v>
       </c>
       <c r="M18" s="22" t="s">
         <v>25</v>
       </c>
       <c r="N18" s="23"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="82"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="81"/>
     </row>
     <row r="19" spans="1:16" customHeight="1" ht="21">
       <c r="A19" s="47"/>
@@ -1653,13 +1639,13 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="16"/>
-      <c r="L19" s="79"/>
+      <c r="L19" s="78"/>
       <c r="M19" s="22" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="23"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="82"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="81"/>
     </row>
     <row r="20" spans="1:16" customHeight="1" ht="21">
       <c r="A20" s="12"/>
@@ -1675,13 +1661,13 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="16"/>
-      <c r="L20" s="79"/>
+      <c r="L20" s="78"/>
       <c r="M20" s="22" t="s">
         <v>20</v>
       </c>
       <c r="N20" s="23"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="82"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="81"/>
     </row>
     <row r="21" spans="1:16" customHeight="1" ht="21">
       <c r="A21" s="12"/>
@@ -1697,13 +1683,13 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="16"/>
-      <c r="L21" s="80"/>
+      <c r="L21" s="79"/>
       <c r="M21" s="22" t="s">
         <v>14</v>
       </c>
       <c r="N21" s="23"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="82"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="81"/>
     </row>
     <row r="22" spans="1:16" customHeight="1" ht="21">
       <c r="A22" s="47"/>
@@ -1725,7 +1711,7 @@
       </c>
       <c r="N22" s="25"/>
       <c r="O22" s="63"/>
-      <c r="P22" s="83"/>
+      <c r="P22" s="82"/>
     </row>
     <row r="23" spans="1:16" customHeight="1" ht="21">
       <c r="A23" s="12"/>
@@ -1746,8 +1732,8 @@
         <v>27</v>
       </c>
       <c r="N23" s="25"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="85"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="84"/>
     </row>
     <row r="24" spans="1:16" customHeight="1" ht="21">
       <c r="A24" s="12"/>
@@ -1768,8 +1754,8 @@
         <v>20</v>
       </c>
       <c r="N24" s="25"/>
-      <c r="O24" s="84"/>
-      <c r="P24" s="85"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="84"/>
     </row>
     <row r="25" spans="1:16" customHeight="1" ht="21">
       <c r="A25" s="47"/>
@@ -1790,8 +1776,8 @@
         <v>14</v>
       </c>
       <c r="N25" s="25"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="83"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="82"/>
     </row>
     <row r="26" spans="1:16" customHeight="1" ht="21">
       <c r="A26" s="12"/>
@@ -1807,13 +1793,13 @@
       </c>
       <c r="J26" s="59"/>
       <c r="K26" s="43"/>
-      <c r="L26" s="78"/>
+      <c r="L26" s="77"/>
       <c r="M26" s="22" t="s">
         <v>25</v>
       </c>
       <c r="N26" s="23"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="82"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="81"/>
     </row>
     <row r="27" spans="1:16" customHeight="1" ht="21">
       <c r="A27" s="12"/>
@@ -1829,13 +1815,13 @@
       </c>
       <c r="J27" s="59"/>
       <c r="K27" s="43"/>
-      <c r="L27" s="79"/>
+      <c r="L27" s="78"/>
       <c r="M27" s="22" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="23"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="82"/>
+      <c r="O27" s="80"/>
+      <c r="P27" s="81"/>
     </row>
     <row r="28" spans="1:16" customHeight="1" ht="21">
       <c r="A28" s="47"/>
@@ -1851,13 +1837,13 @@
       </c>
       <c r="J28" s="59"/>
       <c r="K28" s="28"/>
-      <c r="L28" s="79"/>
+      <c r="L28" s="78"/>
       <c r="M28" s="22" t="s">
         <v>20</v>
       </c>
       <c r="N28" s="23"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="82"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="81"/>
     </row>
     <row r="29" spans="1:16" customHeight="1" ht="21">
       <c r="A29" s="12"/>
@@ -1873,13 +1859,13 @@
       </c>
       <c r="J29" s="59"/>
       <c r="K29" s="28"/>
-      <c r="L29" s="80"/>
+      <c r="L29" s="79"/>
       <c r="M29" s="22" t="s">
         <v>14</v>
       </c>
       <c r="N29" s="23"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="82"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="81"/>
     </row>
     <row r="30" spans="1:16" customHeight="1" ht="21">
       <c r="A30" s="12"/>
@@ -1982,8 +1968,8 @@
       <c r="L34" s="67"/>
       <c r="M34" s="26"/>
       <c r="N34" s="27"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="72"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
     </row>
     <row r="35" spans="1:16" customHeight="1" ht="21">
       <c r="A35" s="12"/>
@@ -2000,8 +1986,8 @@
       <c r="L35" s="68"/>
       <c r="M35" s="26"/>
       <c r="N35" s="27"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="74"/>
+      <c r="O35" s="72"/>
+      <c r="P35" s="73"/>
     </row>
     <row r="36" spans="1:16" customHeight="1" ht="21">
       <c r="A36" s="12"/>
@@ -2012,14 +1998,14 @@
       <c r="F36" s="15"/>
       <c r="G36" s="57"/>
       <c r="H36" s="13"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="77"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="76"/>
       <c r="K36" s="48"/>
       <c r="L36" s="69"/>
       <c r="M36" s="26"/>
       <c r="N36" s="27"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="74"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="73"/>
     </row>
     <row r="37" spans="1:16" customHeight="1" ht="21">
       <c r="A37" s="12"/>
@@ -2046,8 +2032,8 @@
       </c>
       <c r="M37" s="26"/>
       <c r="N37" s="27"/>
-      <c r="O37" s="75"/>
-      <c r="P37" s="72"/>
+      <c r="O37" s="74"/>
+      <c r="P37" s="71"/>
     </row>
     <row r="38" spans="1:16" customHeight="1" ht="21">
       <c r="A38" s="12"/>
@@ -2063,11 +2049,11 @@
       <c r="I38" s="38"/>
       <c r="J38" s="38"/>
       <c r="K38" s="39"/>
-      <c r="L38" s="67"/>
+      <c r="L38" s="39"/>
       <c r="M38" s="26"/>
       <c r="N38" s="27"/>
-      <c r="O38" s="71"/>
-      <c r="P38" s="72"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
     </row>
     <row r="39" spans="1:16" customHeight="1" ht="21">
       <c r="A39" s="12"/>
@@ -2083,11 +2069,11 @@
       <c r="I39" s="38"/>
       <c r="J39" s="38"/>
       <c r="K39" s="39"/>
-      <c r="L39" s="68"/>
+      <c r="L39" s="39"/>
       <c r="M39" s="26"/>
       <c r="N39" s="27"/>
-      <c r="O39" s="73"/>
-      <c r="P39" s="74"/>
+      <c r="O39" s="72"/>
+      <c r="P39" s="73"/>
     </row>
     <row r="40" spans="1:16" customHeight="1" ht="21">
       <c r="A40" s="12"/>
@@ -2103,11 +2089,11 @@
       <c r="I40" s="38"/>
       <c r="J40" s="38"/>
       <c r="K40" s="39"/>
-      <c r="L40" s="69"/>
+      <c r="L40" s="39"/>
       <c r="M40" s="26"/>
       <c r="N40" s="27"/>
-      <c r="O40" s="73"/>
-      <c r="P40" s="74"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="73"/>
     </row>
     <row r="41" spans="1:16" customHeight="1" ht="21">
       <c r="A41" s="12"/>
@@ -2123,11 +2109,11 @@
       <c r="I41" s="38"/>
       <c r="J41" s="38"/>
       <c r="K41" s="39"/>
-      <c r="L41" s="70"/>
+      <c r="L41" s="39"/>
       <c r="M41" s="26"/>
       <c r="N41" s="27"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="72"/>
+      <c r="O41" s="74"/>
+      <c r="P41" s="71"/>
     </row>
     <row r="1048576" spans="1:16">
       <c r="G1048576" s="53" t="s">
@@ -2198,7 +2184,6 @@
     <mergeCell ref="O28:P28"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="O29:P29"/>
-    <mergeCell ref="L38:L41"/>
     <mergeCell ref="O38:P38"/>
     <mergeCell ref="O39:P39"/>
     <mergeCell ref="O40:P40"/>
@@ -2207,7 +2192,6 @@
     <mergeCell ref="L30:L33"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:L37"/>
     <mergeCell ref="O34:P34"/>
     <mergeCell ref="O35:P35"/>
     <mergeCell ref="O36:P36"/>

--- a/templates/excel/yukleme_plani_template.xlsx
+++ b/templates/excel/yukleme_plani_template.xlsx
@@ -2203,6 +2203,13 @@
     <mergeCell ref="O32:P32"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="O33:P33"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I24:J24"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
